--- a/outputs/daily/hr_rankings_2026-10-15.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-15.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.6</v>
+        <v>62.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -888,10 +888,10 @@
         <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,12 +1154,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,11 +1178,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.9</v>
+        <v>61.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1206,10 +1202,10 @@
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1476,12 +1468,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.6</v>
+        <v>58.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,7 +1506,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1524,10 +1516,10 @@
         <v>35.6</v>
       </c>
       <c r="R4" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1541,39 +1533,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1769,24 +1757,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -1794,31 +1782,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.2</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,26 +1820,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R5" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>48.3</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1859,42 +1847,38 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1911,12 +1895,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1926,12 +1910,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1941,102 +1925,102 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
+          <t>0.3329</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>74.25</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>44.59</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>31.29</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>0.3296</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>72.62</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2087,12 +2071,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2112,12 +2096,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.1</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,26 +2134,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>35.6</v>
       </c>
       <c r="R6" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2177,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2234,22 +2214,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2259,67 +2239,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2354,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2405,24 +2385,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -2430,31 +2410,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.4</v>
+        <v>54.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,26 +2448,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>45.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R7" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>48.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2495,42 +2475,38 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2547,27 +2523,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2577,102 +2553,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2723,12 +2699,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2738,7 +2714,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2748,12 +2724,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.7</v>
+        <v>52.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,68 +2762,62 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>55.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q8" t="n">
         <v>39.5</v>
       </c>
       <c r="R8" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
+        <v>78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>100</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2867,154 +2837,154 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/26, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>37.34</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>89.87</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>98.5265</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4311</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.1567</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3363</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>69.46</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>33.31</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>90.32</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>101.2892</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.4781</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>0.2366</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>0.3565</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>71.24</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>51.36</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.2347</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>78</t>
@@ -3026,56 +2996,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Dodger +19; elite sheet line vs Cameron LHH split</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3108,12 +3038,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3132,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3076,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3156,10 +3086,10 @@
         <v>35.6</v>
       </c>
       <c r="R9" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -3173,39 +3103,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3276,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3401,24 +3327,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -3426,31 +3352,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.2</v>
+        <v>51.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,26 +3390,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.7</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R10" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>29.2</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3491,42 +3417,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3543,12 +3465,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3558,12 +3480,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3573,102 +3495,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3719,24 +3641,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -3744,31 +3666,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,26 +3704,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R11" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3809,42 +3731,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3861,27 +3779,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3891,102 +3809,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,24 +3955,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -4062,31 +3980,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.8</v>
+        <v>51.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>39.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>35.6</v>
-      </c>
       <c r="R12" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,42 +4045,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4184,22 +4098,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,102 +4123,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4380,12 +4294,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.1</v>
+        <v>48.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,7 +4332,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4428,10 +4342,10 @@
         <v>39.5</v>
       </c>
       <c r="R13" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
@@ -4445,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4622,7 +4532,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4673,22 +4583,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4698,31 +4608,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,69 +4646,67 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>38.2</v>
+        <v>33.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R14" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>25.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
-        <v>50</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>57</v>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4815,175 +4723,215 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/25, 0 HR</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>37.53</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>88.98</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>98.7109</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.1598</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.3433</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>71.58</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>20.59</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>42.96</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>34.24</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.1658</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>UNIQLO Field at Dodger Stadium</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>43.95</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>89.29</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>100.9775</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>0.4012</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>0.1674</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0.3146</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>73.23</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>32.32</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>0.3296</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>0.1357</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="inlineStr"/>
-      <c r="BX14" t="inlineStr"/>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4996,7 +4944,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5006,7 +4954,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5016,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.8</v>
+        <v>44.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,7 +5002,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5064,10 +5012,10 @@
         <v>39.5</v>
       </c>
       <c r="R15" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -5076,46 +5024,40 @@
         <v>28.5</v>
       </c>
       <c r="V15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>49</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5260,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5294,56 +5236,16 @@
         </is>
       </c>
       <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>Tiny sample; park helps but not core parlay leg</t>
-        </is>
-      </c>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5351,12 +5253,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5366,7 +5268,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5376,12 +5278,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5400,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.6</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5414,68 +5316,62 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>33.9</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
         <v>39.5</v>
       </c>
       <c r="R16" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
+        <v>78</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V16" t="n">
         <v>50</v>
       </c>
-      <c r="U16" t="n">
-        <v>12</v>
-      </c>
-      <c r="V16" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>57</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5495,12 +5391,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5510,12 +5406,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5525,67 +5421,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5620,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5654,56 +5550,16 @@
         </is>
       </c>
       <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5711,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5736,12 +5592,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5760,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.9</v>
+        <v>37.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5774,26 +5630,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="R17" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5801,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5853,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5868,12 +5720,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5883,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5978,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6029,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6054,12 +5906,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -6078,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.8</v>
+        <v>37.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6092,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
         <v>35.6</v>
       </c>
       <c r="R18" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6119,42 +5971,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -6171,12 +6019,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6186,12 +6034,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6201,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6296,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6347,12 +6195,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6372,12 +6220,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6396,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34</v>
+        <v>36.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6410,26 +6258,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
         <v>35.6</v>
       </c>
       <c r="R19" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6437,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6489,12 +6333,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6504,12 +6348,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6519,67 +6363,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6614,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7096,12 +6940,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7120,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.6</v>
+        <v>62.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7134,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7144,10 +6988,10 @@
         <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7161,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7338,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7414,12 +7254,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7438,11 +7278,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.9</v>
+        <v>61.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -7452,7 +7292,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7462,10 +7302,10 @@
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -7479,39 +7319,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7656,7 +7492,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7732,12 +7568,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7756,7 +7592,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.6</v>
+        <v>58.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7770,7 +7606,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7780,10 +7616,10 @@
         <v>35.6</v>
       </c>
       <c r="R4" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -7797,39 +7633,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7974,7 +7806,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8025,24 +7857,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -8050,31 +7882,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.2</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8088,26 +7920,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R5" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>48.3</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -8115,42 +7947,38 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -8167,12 +7995,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -8182,12 +8010,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -8197,102 +8025,102 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
+          <t>0.3329</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>74.25</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>44.59</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>31.29</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>0.3296</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>72.62</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8343,12 +8171,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8368,12 +8196,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8392,7 +8220,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.1</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8406,26 +8234,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>35.6</v>
       </c>
       <c r="R6" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8433,39 +8261,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8490,22 +8314,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8515,67 +8339,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8610,7 +8434,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8661,24 +8485,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -8686,31 +8510,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.4</v>
+        <v>54.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8724,26 +8548,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>45.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R7" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>48.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8751,42 +8575,38 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8803,27 +8623,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8833,102 +8653,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8979,12 +8799,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8994,7 +8814,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9004,12 +8824,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -9028,7 +8848,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.7</v>
+        <v>52.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9042,68 +8862,62 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>55.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q8" t="n">
         <v>39.5</v>
       </c>
       <c r="R8" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
+        <v>78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>100</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9123,154 +8937,154 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/26, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>37.34</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>89.87</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>98.5265</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4311</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.1567</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3363</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>69.46</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>33.31</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>90.32</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>101.2892</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.4781</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>0.2366</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>0.3565</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>71.24</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>51.36</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.2347</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>78</t>
@@ -9282,56 +9096,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Dodger +19; elite sheet line vs Cameron LHH split</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9364,12 +9138,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9388,7 +9162,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9402,7 +9176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9412,10 +9186,10 @@
         <v>35.6</v>
       </c>
       <c r="R9" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -9429,39 +9203,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9606,7 +9376,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9657,24 +9427,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -9682,31 +9452,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.2</v>
+        <v>51.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9720,26 +9490,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.7</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R10" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>29.2</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9747,42 +9517,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9799,12 +9565,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -9814,12 +9580,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9829,102 +9595,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9975,24 +9741,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -10000,31 +9766,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -10038,26 +9804,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R11" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -10065,42 +9831,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -10117,27 +9879,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -10147,102 +9909,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10293,24 +10055,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -10318,31 +10080,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.8</v>
+        <v>51.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10356,26 +10118,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>39.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>35.6</v>
-      </c>
       <c r="R12" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10383,42 +10145,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10440,22 +10198,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10465,102 +10223,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10636,12 +10394,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10660,7 +10418,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.1</v>
+        <v>48.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10674,7 +10432,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -10684,10 +10442,10 @@
         <v>39.5</v>
       </c>
       <c r="R13" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
@@ -10701,39 +10459,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10878,7 +10632,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10929,22 +10683,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -10954,31 +10708,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10992,69 +10746,67 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>38.2</v>
+        <v>33.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R14" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>25.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
-        <v>50</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>57</v>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -11071,175 +10823,215 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/25, 0 HR</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>37.53</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>88.98</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>98.7109</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.1598</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.3433</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>71.58</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>20.59</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>42.96</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>34.24</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.1658</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>UNIQLO Field at Dodger Stadium</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>43.95</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>89.29</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>100.9775</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>0.4012</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>0.1674</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0.3146</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>73.23</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>32.32</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>0.3296</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>0.1357</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="inlineStr"/>
-      <c r="BX14" t="inlineStr"/>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11252,7 +11044,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11262,7 +11054,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11272,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11296,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.8</v>
+        <v>44.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11310,7 +11102,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11320,10 +11112,10 @@
         <v>39.5</v>
       </c>
       <c r="R15" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -11332,46 +11124,40 @@
         <v>28.5</v>
       </c>
       <c r="V15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>49</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11516,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11550,56 +11336,16 @@
         </is>
       </c>
       <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>Tiny sample; park helps but not core parlay leg</t>
-        </is>
-      </c>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11607,12 +11353,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11622,7 +11368,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11632,12 +11378,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11656,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.6</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11670,68 +11416,62 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>33.9</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
         <v>39.5</v>
       </c>
       <c r="R16" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
+        <v>78</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V16" t="n">
         <v>50</v>
       </c>
-      <c r="U16" t="n">
-        <v>12</v>
-      </c>
-      <c r="V16" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>57</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11751,12 +11491,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11766,12 +11506,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11781,67 +11521,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11876,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11910,56 +11650,16 @@
         </is>
       </c>
       <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11967,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11992,12 +11692,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -12016,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.9</v>
+        <v>37.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -12030,26 +11730,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="R17" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -12057,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -12109,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -12124,12 +11820,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -12139,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12234,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12285,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12310,12 +12006,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12334,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.8</v>
+        <v>37.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12348,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
         <v>35.6</v>
       </c>
       <c r="R18" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12375,42 +12071,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -12427,12 +12119,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12442,12 +12134,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12457,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12552,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12603,12 +12295,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12628,12 +12320,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12652,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34</v>
+        <v>36.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12666,26 +12358,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
         <v>35.6</v>
       </c>
       <c r="R19" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12693,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12745,12 +12433,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -12760,12 +12448,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12775,67 +12463,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12870,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
